--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488248_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488248_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>14.7919</v>
+        <v>12.5679</v>
       </c>
       <c r="E2" t="n">
-        <v>12.0935</v>
+        <v>10.1896</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6984</v>
+        <v>2.3783</v>
       </c>
       <c r="G2" t="n">
         <v>5.4554</v>
@@ -610,13 +610,13 @@
         <v>2.9646</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7981</v>
+        <v>2.5741</v>
       </c>
       <c r="T2" t="n">
-        <v>3.6946</v>
+        <v>1.7907</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1035</v>
+        <v>0.7834</v>
       </c>
       <c r="V2" t="n">
         <v>1.5738</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4142</v>
+        <v>4.9356</v>
       </c>
       <c r="E3" t="n">
-        <v>3.235</v>
+        <v>3.4856</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1792</v>
+        <v>1.45</v>
       </c>
       <c r="G3" t="n">
         <v>2.7426</v>
@@ -688,13 +688,13 @@
         <v>2.7793</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7451</v>
+        <v>1.2665</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5609</v>
+        <v>0.8114</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1843</v>
+        <v>0.4551</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.656</v>
+        <v>3.5329</v>
       </c>
       <c r="E4" t="n">
         <v>1.1454</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5106</v>
+        <v>2.3875</v>
       </c>
       <c r="G4" t="n">
         <v>1.961</v>
@@ -766,13 +766,13 @@
         <v>2.594</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8802</v>
+        <v>1.7571</v>
       </c>
       <c r="T4" t="n">
         <v>1.1926</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6877</v>
+        <v>0.5645</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4093</v>
+        <v>2.3118</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0945</v>
+        <v>2.2679</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3147</v>
+        <v>0.0439</v>
       </c>
       <c r="G5" t="n">
         <v>-2.0972</v>
@@ -844,13 +844,13 @@
         <v>0.3706</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9882</v>
+        <v>0.8907</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8156</v>
+        <v>0.9889</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1726</v>
+        <v>-0.0982</v>
       </c>
       <c r="V5" t="n">
         <v>3.1477</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4493</v>
+        <v>1.9209</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8362</v>
+        <v>2.1847</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3869</v>
+        <v>-0.2638</v>
       </c>
       <c r="G6" t="n">
         <v>1.1608</v>
@@ -922,13 +922,13 @@
         <v>0.7411</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4526</v>
+        <v>0.019</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2524</v>
+        <v>0.0961</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2002</v>
+        <v>-0.0771</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. LÓPEZ RUIZ</t>
+          <t>R. VARELA SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9441000000000001</v>
+        <v>1.4204</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.2716</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3221</v>
+        <v>-0.3813</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6221</v>
+        <v>0.6529</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.0859</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3221</v>
+        <v>0.0859</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6221</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.1857</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.4671</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.6529</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.4632</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.4781</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.0149</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. VARELA SANCHEZ</t>
+          <t>A. VALDERRAMA VIDAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6851</v>
+        <v>1.3115</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0235</v>
+        <v>1.229</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7086</v>
+        <v>0.0825</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2716</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3813</v>
+        <v>0.4793</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6529</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0859</v>
+        <v>0.8285</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0859</v>
+        <v>1.46</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.6315</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1857</v>
+        <v>-0.8961</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4671</v>
+        <v>-0.9807</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6529</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3706</v>
+        <v>0.9264</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3706</v>
+        <v>0.9264</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2721</v>
+        <v>0.4526</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1094</v>
+        <v>0.4004</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1627</v>
+        <v>0.0522</v>
       </c>
       <c r="V8" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA VIDAL</t>
+          <t>J. LÓPEZ RUIZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6211</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3908</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2303</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.06759999999999999</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4793</v>
+        <v>0.3221</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5469000000000001</v>
+        <v>0.6221</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8285</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>1.46</v>
+        <v>0.3221</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6315</v>
+        <v>0.6221</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8961</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9807</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.08459999999999999</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2378</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4377</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1999</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. RODRIGUEZ GALLARDO</t>
+          <t>J. LOPEZ RUIZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0256</v>
+        <v>0.4135</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0404</v>
+        <v>-0.2189</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.066</v>
+        <v>0.6324</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.189</v>
+        <v>-1.7163</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1735</v>
+        <v>-1.5796</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3626</v>
+        <v>-0.1367</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0951</v>
+        <v>-0.6289</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0429</v>
+        <v>-0.6918</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0522</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2841</v>
+        <v>-1.0874</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1306</v>
+        <v>-0.8878</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4147</v>
+        <v>-0.1996</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1853</v>
+        <v>1.8529</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1853</v>
+        <v>1.8529</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0219</v>
+        <v>0.277</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0547</v>
+        <v>0.4101</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0328</v>
+        <v>-0.1331</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. LLANO ABASCAL</t>
+          <t>D. RODRIGUEZ GALLARDO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1509</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5474</v>
+        <v>0.0951</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6983</v>
+        <v>-0.0168</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.7326</v>
+        <v>-0.189</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0752</v>
+        <v>0.1735</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6574</v>
+        <v>-0.3626</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.8742</v>
+        <v>0.0951</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2628</v>
+        <v>0.0429</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0.0522</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8584000000000001</v>
+        <v>-0.2841</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8124</v>
+        <v>0.1306</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.046</v>
+        <v>-0.4147</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3706</v>
+        <v>0.1853</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3706</v>
+        <v>0.1853</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9523</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1627</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2104</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. LOPEZ RUIZ</t>
+          <t>I. LLANO ABASCAL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.7141</v>
+        <v>-0.5125</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1002</v>
+        <v>0.2104</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3862</v>
+        <v>-0.7229</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.7163</v>
+        <v>-2.7326</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5796</v>
+        <v>-2.0752</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1367</v>
+        <v>-0.6574</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6289</v>
+        <v>-1.8742</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6918</v>
+        <v>-1.2628</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06279999999999999</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.0874</v>
+        <v>-0.8584000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8878</v>
+        <v>-0.8124</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1996</v>
+        <v>-0.046</v>
       </c>
       <c r="P12" t="n">
-        <v>1.8529</v>
+        <v>0.3706</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8529</v>
+        <v>0.3706</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8506</v>
+        <v>0.5907</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4713</v>
+        <v>0.8257</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3793</v>
+        <v>-0.235</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.116</v>
+        <v>-1.8594</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1102</v>
+        <v>-2.9028</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9942</v>
+        <v>1.0434</v>
       </c>
       <c r="G13" t="n">
         <v>-1.2461</v>
@@ -1468,13 +1468,13 @@
         <v>2.9646</v>
       </c>
       <c r="S13" t="n">
-        <v>1.7427</v>
+        <v>1.9993</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1379</v>
+        <v>1.3452</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6048</v>
+        <v>0.6541</v>
       </c>
       <c r="V13" t="n">
         <v>-0.945</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.8287</v>
+        <v>-2.3822</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.3891</v>
+        <v>0.0573</v>
       </c>
       <c r="F14" t="n">
         <v>-2.4395</v>
@@ -1546,10 +1546,10 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1306</v>
+        <v>0.577</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3793</v>
+        <v>0.8257</v>
       </c>
       <c r="U14" t="n">
         <v>-0.2487</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>24.1357</v>
+        <v>24.6828</v>
       </c>
       <c r="E15" t="n">
-        <v>18.7043</v>
+        <v>19.2514</v>
       </c>
       <c r="F15" t="n">
-        <v>5.431500000000002</v>
+        <v>5.431399999999999</v>
       </c>
       <c r="G15" t="n">
         <v>3.786299999999999</v>
@@ -1606,10 +1606,10 @@
         <v>1.3428</v>
       </c>
       <c r="M15" t="n">
-        <v>-9.568199999999999</v>
+        <v>-9.568199999999997</v>
       </c>
       <c r="N15" t="n">
-        <v>-9.5311</v>
+        <v>-9.531100000000002</v>
       </c>
       <c r="O15" t="n">
         <v>-0.03699999999999999</v>
@@ -1624,13 +1624,13 @@
         <v>16.6759</v>
       </c>
       <c r="S15" t="n">
-        <v>10.4022</v>
+        <v>10.9493</v>
       </c>
       <c r="T15" t="n">
-        <v>8.6181</v>
+        <v>9.164899999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>1.7843</v>
+        <v>1.7844</v>
       </c>
       <c r="V15" t="n">
         <v>3.4621</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8094</v>
+        <v>2.6634</v>
       </c>
       <c r="E16" t="n">
-        <v>5.1289</v>
+        <v>4.8351</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.3195</v>
+        <v>-2.1717</v>
       </c>
       <c r="G16" t="n">
         <v>5.5068</v>
@@ -1702,13 +1702,13 @@
         <v>1.1117</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6974</v>
+        <v>-0.8434</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0037</v>
+        <v>-0.2975</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6937</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2589</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. VALIENTE RODRIGUEZ</t>
+          <t>A. CHAPARRO CARRASCO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0252</v>
+        <v>0.8666</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4901</v>
+        <v>2.6087</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4648</v>
+        <v>-1.7421</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1053</v>
+        <v>2.7461</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0608</v>
+        <v>3.1563</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9555</v>
+        <v>-0.4102</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1692</v>
+        <v>4.4832</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2107</v>
+        <v>4.4097</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0415</v>
+        <v>0.0735</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0639</v>
+        <v>-1.7371</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8501</v>
+        <v>-1.2534</v>
       </c>
       <c r="O17" t="n">
-        <v>0.914</v>
+        <v>-0.4837</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7411</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7411</v>
+        <v>1.297</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.24</v>
+        <v>-1.6561</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4004</v>
+        <v>-0.3541</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6404</v>
+        <v>-1.302</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6294</v>
+        <v>1.2589</v>
       </c>
       <c r="W17" t="n">
         <v>1.2589</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Á. CHAPARRO CARRASCO</t>
+          <t>S. VALIENTE RODRIGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6221</v>
+        <v>0.7641</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6221</v>
+        <v>1.0984</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-0.3343</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6221</v>
+        <v>-0.1053</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-1.0608</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6221</v>
+        <v>0.9555</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6221</v>
+        <v>-0.1692</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-0.2107</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6221</v>
+        <v>0.0415</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>0.0639</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.8501</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.914</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0.5011</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0.5099</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. CHAPARRO CARRASCO</t>
+          <t>Á. CHAPARRO CARRASCO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0159</v>
+        <v>0.6221</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9232</v>
+        <v>0.6221</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9391</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7461</v>
+        <v>0.6221</v>
       </c>
       <c r="H19" t="n">
-        <v>3.1563</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4102</v>
+        <v>0.6221</v>
       </c>
       <c r="J19" t="n">
-        <v>4.4832</v>
+        <v>0.6221</v>
       </c>
       <c r="K19" t="n">
-        <v>4.4097</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0735</v>
+        <v>0.6221</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7371</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4837</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.4823</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.297</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.5386</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0396</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.499</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0973</v>
+        <v>-0.3858</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.713</v>
+        <v>-0.6151</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6158</v>
+        <v>0.2293</v>
       </c>
       <c r="G20" t="n">
         <v>0.0124</v>
@@ -2014,13 +2014,13 @@
         <v>1.4823</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6656</v>
+        <v>-0.9540999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.7564</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1887</v>
+        <v>-0.1977</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0991</v>
+        <v>-1.4335</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4782</v>
+        <v>-0.9679</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6208</v>
+        <v>-0.4656</v>
       </c>
       <c r="G21" t="n">
         <v>0.9006</v>
@@ -2092,13 +2092,13 @@
         <v>1.297</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1289</v>
+        <v>-1.4633</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6703</v>
+        <v>0.1806</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.7992</v>
+        <v>-1.644</v>
       </c>
       <c r="V21" t="n">
         <v>-0.315</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5392</v>
+        <v>-1.49</v>
       </c>
       <c r="E22" t="n">
         <v>-0.9602000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.579</v>
+        <v>-0.5298</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3514</v>
@@ -2170,13 +2170,13 @@
         <v>0.1853</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0766</v>
+        <v>-0.0274</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1094</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0328</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>0.63</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.784</v>
+        <v>-1.8343</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0009</v>
+        <v>0.1967</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7848</v>
+        <v>-2.031</v>
       </c>
       <c r="G23" t="n">
         <v>-1.0906</v>
@@ -2248,13 +2248,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6193</v>
+        <v>-0.6696</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1057</v>
+        <v>0.3016</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.725</v>
+        <v>-0.9712</v>
       </c>
       <c r="V23" t="n">
         <v>-0.63</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.5513</v>
+        <v>-5.029</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4469</v>
+        <v>-2.0552</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.1044</v>
+        <v>-2.9738</v>
       </c>
       <c r="G24" t="n">
         <v>-2.7131</v>
@@ -2326,13 +2326,13 @@
         <v>1.1117</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8381</v>
+        <v>-0.3159</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6566</v>
+        <v>-0.2649</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1816</v>
+        <v>-0.051</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2589</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>I. FERNANDEZ MEGIAS</t>
+          <t>J. ROSA CABRERA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.0509</v>
+        <v>-5.595</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.6858</v>
+        <v>-3.9412</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.3651</v>
+        <v>-1.6538</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.9129</v>
+        <v>-3.2801</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.836</v>
+        <v>-1.489</v>
       </c>
       <c r="I25" t="n">
-        <v>0.923</v>
+        <v>-1.7911</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7092000000000001</v>
+        <v>-2.9237</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.2198</v>
+        <v>-0.3952</v>
       </c>
       <c r="L25" t="n">
-        <v>1.929</v>
+        <v>-2.5285</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.6221</v>
+        <v>-0.3564</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.6161</v>
+        <v>-1.0938</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.006</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.7057</v>
+        <v>0.1853</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.7057</v>
+        <v>-0.9264</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4322</v>
+        <v>-1.2414</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0037</v>
+        <v>-0.0911</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4285</v>
+        <v>-1.1503</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
       <c r="W25" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.3144</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. ROSA CABRERA</t>
+          <t>I. FERNANDEZ MEGIAS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.2152</v>
+        <v>-5.9765</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.4309</v>
+        <v>-2.7837</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.7844</v>
+        <v>-3.1927</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.2801</v>
+        <v>-1.9129</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.489</v>
+        <v>-2.836</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.7911</v>
+        <v>0.923</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.9237</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.3952</v>
+        <v>-1.2198</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.5285</v>
+        <v>1.929</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.3564</v>
+        <v>-2.6221</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.0938</v>
+        <v>-1.6161</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7374000000000001</v>
+        <v>-1.006</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1853</v>
+        <v>-3.7057</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.9264</v>
+        <v>-3.7057</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.8616</v>
+        <v>-0.3578</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5807</v>
+        <v>-0.1016</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.2809</v>
+        <v>-0.2562</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.2589</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-6.2396</v>
+        <v>-6.6548</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.8814</v>
+        <v>-3.469</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.3582</v>
+        <v>-3.1858</v>
       </c>
       <c r="G27" t="n">
         <v>-3.1209</v>
@@ -2560,13 +2560,13 @@
         <v>1.297</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.304</v>
+        <v>-1.7192</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2873</v>
+        <v>-0.3003</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.5913</v>
+        <v>-1.4189</v>
       </c>
       <c r="V27" t="n">
         <v>-1.2589</v>
@@ -2593,19 +2593,19 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-24.1358</v>
+        <v>-23.4827</v>
       </c>
       <c r="E28" t="n">
-        <v>-5.4312</v>
+        <v>-5.4313</v>
       </c>
       <c r="F28" t="n">
-        <v>-18.7043</v>
+        <v>-18.0513</v>
       </c>
       <c r="G28" t="n">
         <v>-3.786299999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>-2.4805</v>
+        <v>-2.480500000000001</v>
       </c>
       <c r="I28" t="n">
         <v>-1.3058</v>
@@ -2638,13 +2638,13 @@
         <v>10.1907</v>
       </c>
       <c r="S28" t="n">
-        <v>-10.4023</v>
+        <v>-9.7493</v>
       </c>
       <c r="T28" t="n">
-        <v>-1.7843</v>
+        <v>-1.7844</v>
       </c>
       <c r="U28" t="n">
-        <v>-8.6181</v>
+        <v>-7.964999999999999</v>
       </c>
       <c r="V28" t="n">
         <v>-3.4623</v>
